--- a/Lista_de_Livros_com_genero.xlsx
+++ b/Lista_de_Livros_com_genero.xlsx
@@ -1,20 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TEMP\MinhaBiblioteca\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7265717B-C93C-459B-8FE2-CCCC3E3ED031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="goodreads_library_export" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">goodreads_library_export!$A$1:$N$341</definedName>
+  </definedNames>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="858">
   <si>
     <t>Título</t>
   </si>
@@ -2585,9 +2608,6 @@
   </si>
   <si>
     <t>lido</t>
-  </si>
-  <si>
-    <t>lendo</t>
   </si>
   <si>
     <t>Não</t>
@@ -2596,11 +2616,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2629,20 +2649,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2684,7 +2713,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2716,9 +2745,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2750,6 +2797,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2925,11 +2990,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N341"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2973,7 +3054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3014,10 +3095,10 @@
         <v>856</v>
       </c>
       <c r="N2" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3058,10 +3139,10 @@
         <v>856</v>
       </c>
       <c r="N3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3102,10 +3183,10 @@
         <v>856</v>
       </c>
       <c r="N4" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3143,10 +3224,10 @@
         <v>856</v>
       </c>
       <c r="N5" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -3187,10 +3268,10 @@
         <v>856</v>
       </c>
       <c r="N6" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -3231,10 +3312,10 @@
         <v>856</v>
       </c>
       <c r="N7" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -3275,10 +3356,10 @@
         <v>856</v>
       </c>
       <c r="N8" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -3319,10 +3400,10 @@
         <v>856</v>
       </c>
       <c r="N9" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -3363,10 +3444,10 @@
         <v>856</v>
       </c>
       <c r="N10" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -3407,10 +3488,10 @@
         <v>856</v>
       </c>
       <c r="N11" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3451,10 +3532,10 @@
         <v>856</v>
       </c>
       <c r="N12" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -3495,10 +3576,10 @@
         <v>856</v>
       </c>
       <c r="N13" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3536,10 +3617,10 @@
         <v>856</v>
       </c>
       <c r="N14" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -3577,10 +3658,10 @@
         <v>856</v>
       </c>
       <c r="N15" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -3621,10 +3702,10 @@
         <v>856</v>
       </c>
       <c r="N16" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -3665,10 +3746,10 @@
         <v>856</v>
       </c>
       <c r="N17" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -3706,10 +3787,10 @@
         <v>856</v>
       </c>
       <c r="N18" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -3750,10 +3831,10 @@
         <v>856</v>
       </c>
       <c r="N19" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3791,10 +3872,10 @@
         <v>856</v>
       </c>
       <c r="N20" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3835,10 +3916,10 @@
         <v>856</v>
       </c>
       <c r="N21" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -3879,10 +3960,10 @@
         <v>856</v>
       </c>
       <c r="N22" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -3920,10 +4001,10 @@
         <v>856</v>
       </c>
       <c r="N23" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -3964,10 +4045,10 @@
         <v>856</v>
       </c>
       <c r="N24" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -4008,10 +4089,10 @@
         <v>856</v>
       </c>
       <c r="N25" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -4049,10 +4130,10 @@
         <v>856</v>
       </c>
       <c r="N26" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4093,10 +4174,10 @@
         <v>856</v>
       </c>
       <c r="N27" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -4137,10 +4218,10 @@
         <v>856</v>
       </c>
       <c r="N28" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -4181,10 +4262,10 @@
         <v>856</v>
       </c>
       <c r="N29" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -4225,10 +4306,10 @@
         <v>856</v>
       </c>
       <c r="N30" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -4269,10 +4350,10 @@
         <v>856</v>
       </c>
       <c r="N31" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -4313,10 +4394,10 @@
         <v>856</v>
       </c>
       <c r="N32" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -4354,10 +4435,10 @@
         <v>856</v>
       </c>
       <c r="N33" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -4398,10 +4479,10 @@
         <v>856</v>
       </c>
       <c r="N34" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -4439,10 +4520,10 @@
         <v>856</v>
       </c>
       <c r="N35" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -4480,10 +4561,10 @@
         <v>856</v>
       </c>
       <c r="N36" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -4524,10 +4605,10 @@
         <v>856</v>
       </c>
       <c r="N37" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -4568,10 +4649,10 @@
         <v>856</v>
       </c>
       <c r="N38" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -4612,10 +4693,10 @@
         <v>856</v>
       </c>
       <c r="N39" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -4656,10 +4737,10 @@
         <v>856</v>
       </c>
       <c r="N40" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -4700,10 +4781,10 @@
         <v>856</v>
       </c>
       <c r="N41" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -4744,10 +4825,10 @@
         <v>856</v>
       </c>
       <c r="N42" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -4788,10 +4869,10 @@
         <v>856</v>
       </c>
       <c r="N43" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -4832,10 +4913,10 @@
         <v>856</v>
       </c>
       <c r="N44" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -4873,10 +4954,10 @@
         <v>856</v>
       </c>
       <c r="N45" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -4917,10 +4998,10 @@
         <v>856</v>
       </c>
       <c r="N46" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -4958,10 +5039,10 @@
         <v>856</v>
       </c>
       <c r="N47" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -4999,10 +5080,10 @@
         <v>856</v>
       </c>
       <c r="N48" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -5040,10 +5121,10 @@
         <v>856</v>
       </c>
       <c r="N49" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -5084,10 +5165,10 @@
         <v>856</v>
       </c>
       <c r="N50" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -5128,10 +5209,10 @@
         <v>856</v>
       </c>
       <c r="N51" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -5169,10 +5250,10 @@
         <v>856</v>
       </c>
       <c r="N52" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>65</v>
       </c>
@@ -5213,10 +5294,10 @@
         <v>856</v>
       </c>
       <c r="N53" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -5257,10 +5338,10 @@
         <v>856</v>
       </c>
       <c r="N54" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -5301,10 +5382,10 @@
         <v>856</v>
       </c>
       <c r="N55" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -5345,10 +5426,10 @@
         <v>856</v>
       </c>
       <c r="N56" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -5389,10 +5470,10 @@
         <v>856</v>
       </c>
       <c r="N57" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -5433,10 +5514,10 @@
         <v>856</v>
       </c>
       <c r="N58" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -5477,10 +5558,10 @@
         <v>856</v>
       </c>
       <c r="N59" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>72</v>
       </c>
@@ -5521,10 +5602,10 @@
         <v>856</v>
       </c>
       <c r="N60" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -5562,10 +5643,10 @@
         <v>856</v>
       </c>
       <c r="N61" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -5606,10 +5687,10 @@
         <v>856</v>
       </c>
       <c r="N62" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>75</v>
       </c>
@@ -5650,10 +5731,10 @@
         <v>856</v>
       </c>
       <c r="N63" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -5694,10 +5775,10 @@
         <v>856</v>
       </c>
       <c r="N64" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -5738,10 +5819,10 @@
         <v>856</v>
       </c>
       <c r="N65" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>78</v>
       </c>
@@ -5782,10 +5863,10 @@
         <v>856</v>
       </c>
       <c r="N66" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>79</v>
       </c>
@@ -5826,10 +5907,10 @@
         <v>856</v>
       </c>
       <c r="N67" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -5867,10 +5948,10 @@
         <v>856</v>
       </c>
       <c r="N68" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -5908,10 +5989,10 @@
         <v>856</v>
       </c>
       <c r="N69" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -5949,10 +6030,10 @@
         <v>856</v>
       </c>
       <c r="N70" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -5993,10 +6074,10 @@
         <v>856</v>
       </c>
       <c r="N71" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -6034,10 +6115,10 @@
         <v>856</v>
       </c>
       <c r="N72" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -6078,10 +6159,10 @@
         <v>856</v>
       </c>
       <c r="N73" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -6122,10 +6203,10 @@
         <v>856</v>
       </c>
       <c r="N74" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -6166,10 +6247,10 @@
         <v>856</v>
       </c>
       <c r="N75" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>88</v>
       </c>
@@ -6210,10 +6291,10 @@
         <v>856</v>
       </c>
       <c r="N76" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>89</v>
       </c>
@@ -6254,10 +6335,10 @@
         <v>856</v>
       </c>
       <c r="N77" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>90</v>
       </c>
@@ -6298,10 +6379,10 @@
         <v>856</v>
       </c>
       <c r="N78" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -6342,10 +6423,10 @@
         <v>856</v>
       </c>
       <c r="N79" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -6383,10 +6464,10 @@
         <v>856</v>
       </c>
       <c r="N80" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>93</v>
       </c>
@@ -6427,10 +6508,10 @@
         <v>856</v>
       </c>
       <c r="N81" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -6471,10 +6552,10 @@
         <v>856</v>
       </c>
       <c r="N82" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>95</v>
       </c>
@@ -6512,10 +6593,10 @@
         <v>856</v>
       </c>
       <c r="N83" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>96</v>
       </c>
@@ -6553,10 +6634,10 @@
         <v>856</v>
       </c>
       <c r="N84" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -6597,10 +6678,10 @@
         <v>856</v>
       </c>
       <c r="N85" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>98</v>
       </c>
@@ -6641,10 +6722,10 @@
         <v>856</v>
       </c>
       <c r="N86" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -6682,10 +6763,10 @@
         <v>856</v>
       </c>
       <c r="N87" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -6726,10 +6807,10 @@
         <v>856</v>
       </c>
       <c r="N88" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -6767,10 +6848,10 @@
         <v>856</v>
       </c>
       <c r="N89" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -6811,10 +6892,10 @@
         <v>856</v>
       </c>
       <c r="N90" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -6855,10 +6936,10 @@
         <v>856</v>
       </c>
       <c r="N91" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -6899,10 +6980,10 @@
         <v>856</v>
       </c>
       <c r="N92" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -6943,10 +7024,10 @@
         <v>856</v>
       </c>
       <c r="N93" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -6987,10 +7068,10 @@
         <v>856</v>
       </c>
       <c r="N94" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -7028,10 +7109,10 @@
         <v>856</v>
       </c>
       <c r="N95" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -7072,10 +7153,10 @@
         <v>856</v>
       </c>
       <c r="N96" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -7116,10 +7197,10 @@
         <v>856</v>
       </c>
       <c r="N97" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -7160,10 +7241,10 @@
         <v>856</v>
       </c>
       <c r="N98" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -7204,10 +7285,10 @@
         <v>856</v>
       </c>
       <c r="N99" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -7248,10 +7329,10 @@
         <v>856</v>
       </c>
       <c r="N100" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -7292,10 +7373,10 @@
         <v>856</v>
       </c>
       <c r="N101" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -7333,10 +7414,10 @@
         <v>856</v>
       </c>
       <c r="N102" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -7377,10 +7458,10 @@
         <v>856</v>
       </c>
       <c r="N103" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -7421,10 +7502,10 @@
         <v>856</v>
       </c>
       <c r="N104" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -7465,10 +7546,10 @@
         <v>856</v>
       </c>
       <c r="N105" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -7509,10 +7590,10 @@
         <v>856</v>
       </c>
       <c r="N106" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -7553,10 +7634,10 @@
         <v>856</v>
       </c>
       <c r="N107" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -7597,10 +7678,10 @@
         <v>856</v>
       </c>
       <c r="N108" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -7641,10 +7722,10 @@
         <v>856</v>
       </c>
       <c r="N109" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -7685,10 +7766,10 @@
         <v>856</v>
       </c>
       <c r="N110" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -7729,10 +7810,10 @@
         <v>856</v>
       </c>
       <c r="N111" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -7773,10 +7854,10 @@
         <v>856</v>
       </c>
       <c r="N112" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>125</v>
       </c>
@@ -7817,10 +7898,10 @@
         <v>856</v>
       </c>
       <c r="N113" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>126</v>
       </c>
@@ -7861,10 +7942,10 @@
         <v>856</v>
       </c>
       <c r="N114" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>127</v>
       </c>
@@ -7905,10 +7986,10 @@
         <v>856</v>
       </c>
       <c r="N115" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>128</v>
       </c>
@@ -7949,10 +8030,10 @@
         <v>856</v>
       </c>
       <c r="N116" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>129</v>
       </c>
@@ -7993,10 +8074,10 @@
         <v>856</v>
       </c>
       <c r="N117" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>130</v>
       </c>
@@ -8037,10 +8118,10 @@
         <v>856</v>
       </c>
       <c r="N118" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>131</v>
       </c>
@@ -8081,10 +8162,10 @@
         <v>856</v>
       </c>
       <c r="N119" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>132</v>
       </c>
@@ -8125,10 +8206,10 @@
         <v>856</v>
       </c>
       <c r="N120" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>133</v>
       </c>
@@ -8169,10 +8250,10 @@
         <v>856</v>
       </c>
       <c r="N121" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>134</v>
       </c>
@@ -8213,10 +8294,10 @@
         <v>856</v>
       </c>
       <c r="N122" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>135</v>
       </c>
@@ -8257,10 +8338,10 @@
         <v>856</v>
       </c>
       <c r="N123" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>136</v>
       </c>
@@ -8301,10 +8382,10 @@
         <v>856</v>
       </c>
       <c r="N124" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>137</v>
       </c>
@@ -8345,10 +8426,10 @@
         <v>856</v>
       </c>
       <c r="N125" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>138</v>
       </c>
@@ -8389,10 +8470,10 @@
         <v>856</v>
       </c>
       <c r="N126" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>139</v>
       </c>
@@ -8433,10 +8514,10 @@
         <v>856</v>
       </c>
       <c r="N127" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>140</v>
       </c>
@@ -8477,10 +8558,10 @@
         <v>856</v>
       </c>
       <c r="N128" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>141</v>
       </c>
@@ -8521,10 +8602,10 @@
         <v>856</v>
       </c>
       <c r="N129" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -8565,10 +8646,10 @@
         <v>856</v>
       </c>
       <c r="N130" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>143</v>
       </c>
@@ -8609,10 +8690,10 @@
         <v>856</v>
       </c>
       <c r="N131" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>144</v>
       </c>
@@ -8653,10 +8734,10 @@
         <v>856</v>
       </c>
       <c r="N132" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>145</v>
       </c>
@@ -8694,10 +8775,10 @@
         <v>856</v>
       </c>
       <c r="N133" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>146</v>
       </c>
@@ -8738,10 +8819,10 @@
         <v>856</v>
       </c>
       <c r="N134" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>147</v>
       </c>
@@ -8782,10 +8863,10 @@
         <v>856</v>
       </c>
       <c r="N135" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>148</v>
       </c>
@@ -8826,10 +8907,10 @@
         <v>856</v>
       </c>
       <c r="N136" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>149</v>
       </c>
@@ -8870,10 +8951,10 @@
         <v>856</v>
       </c>
       <c r="N137" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>150</v>
       </c>
@@ -8914,10 +8995,10 @@
         <v>856</v>
       </c>
       <c r="N138" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>151</v>
       </c>
@@ -8958,10 +9039,10 @@
         <v>856</v>
       </c>
       <c r="N139" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>152</v>
       </c>
@@ -9002,10 +9083,10 @@
         <v>856</v>
       </c>
       <c r="N140" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>153</v>
       </c>
@@ -9046,10 +9127,10 @@
         <v>856</v>
       </c>
       <c r="N141" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>154</v>
       </c>
@@ -9090,10 +9171,10 @@
         <v>856</v>
       </c>
       <c r="N142" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>155</v>
       </c>
@@ -9134,10 +9215,10 @@
         <v>856</v>
       </c>
       <c r="N143" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>156</v>
       </c>
@@ -9178,10 +9259,10 @@
         <v>856</v>
       </c>
       <c r="N144" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>157</v>
       </c>
@@ -9219,10 +9300,10 @@
         <v>856</v>
       </c>
       <c r="N145" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>158</v>
       </c>
@@ -9263,10 +9344,10 @@
         <v>856</v>
       </c>
       <c r="N146" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>159</v>
       </c>
@@ -9307,10 +9388,10 @@
         <v>856</v>
       </c>
       <c r="N147" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>160</v>
       </c>
@@ -9351,10 +9432,10 @@
         <v>856</v>
       </c>
       <c r="N148" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>161</v>
       </c>
@@ -9392,10 +9473,10 @@
         <v>856</v>
       </c>
       <c r="N149" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>162</v>
       </c>
@@ -9433,10 +9514,10 @@
         <v>856</v>
       </c>
       <c r="N150" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>163</v>
       </c>
@@ -9477,10 +9558,10 @@
         <v>856</v>
       </c>
       <c r="N151" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>164</v>
       </c>
@@ -9521,10 +9602,10 @@
         <v>856</v>
       </c>
       <c r="N152" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>165</v>
       </c>
@@ -9565,10 +9646,10 @@
         <v>856</v>
       </c>
       <c r="N153" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>166</v>
       </c>
@@ -9609,10 +9690,10 @@
         <v>856</v>
       </c>
       <c r="N154" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>167</v>
       </c>
@@ -9653,10 +9734,10 @@
         <v>856</v>
       </c>
       <c r="N155" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>168</v>
       </c>
@@ -9697,10 +9778,10 @@
         <v>856</v>
       </c>
       <c r="N156" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>169</v>
       </c>
@@ -9741,10 +9822,10 @@
         <v>856</v>
       </c>
       <c r="N157" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>170</v>
       </c>
@@ -9785,10 +9866,10 @@
         <v>856</v>
       </c>
       <c r="N158" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>171</v>
       </c>
@@ -9826,10 +9907,10 @@
         <v>856</v>
       </c>
       <c r="N159" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>172</v>
       </c>
@@ -9870,10 +9951,10 @@
         <v>856</v>
       </c>
       <c r="N160" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>173</v>
       </c>
@@ -9914,10 +9995,10 @@
         <v>856</v>
       </c>
       <c r="N161" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>174</v>
       </c>
@@ -9958,10 +10039,10 @@
         <v>856</v>
       </c>
       <c r="N162" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>175</v>
       </c>
@@ -10002,10 +10083,10 @@
         <v>856</v>
       </c>
       <c r="N163" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>176</v>
       </c>
@@ -10046,10 +10127,10 @@
         <v>856</v>
       </c>
       <c r="N164" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>177</v>
       </c>
@@ -10090,10 +10171,10 @@
         <v>856</v>
       </c>
       <c r="N165" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>178</v>
       </c>
@@ -10134,10 +10215,10 @@
         <v>856</v>
       </c>
       <c r="N166" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>179</v>
       </c>
@@ -10175,10 +10256,10 @@
         <v>856</v>
       </c>
       <c r="N167" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>180</v>
       </c>
@@ -10219,10 +10300,10 @@
         <v>856</v>
       </c>
       <c r="N168" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>181</v>
       </c>
@@ -10260,10 +10341,10 @@
         <v>856</v>
       </c>
       <c r="N169" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>182</v>
       </c>
@@ -10304,10 +10385,10 @@
         <v>856</v>
       </c>
       <c r="N170" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>183</v>
       </c>
@@ -10348,10 +10429,10 @@
         <v>856</v>
       </c>
       <c r="N171" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>184</v>
       </c>
@@ -10392,10 +10473,10 @@
         <v>856</v>
       </c>
       <c r="N172" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>185</v>
       </c>
@@ -10436,10 +10517,10 @@
         <v>856</v>
       </c>
       <c r="N173" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>186</v>
       </c>
@@ -10480,10 +10561,10 @@
         <v>856</v>
       </c>
       <c r="N174" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>187</v>
       </c>
@@ -10524,10 +10605,10 @@
         <v>856</v>
       </c>
       <c r="N175" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>188</v>
       </c>
@@ -10565,10 +10646,10 @@
         <v>856</v>
       </c>
       <c r="N176" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>189</v>
       </c>
@@ -10609,10 +10690,10 @@
         <v>856</v>
       </c>
       <c r="N177" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>190</v>
       </c>
@@ -10653,10 +10734,10 @@
         <v>856</v>
       </c>
       <c r="N178" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>191</v>
       </c>
@@ -10697,10 +10778,10 @@
         <v>856</v>
       </c>
       <c r="N179" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>192</v>
       </c>
@@ -10741,10 +10822,10 @@
         <v>856</v>
       </c>
       <c r="N180" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>193</v>
       </c>
@@ -10785,10 +10866,10 @@
         <v>856</v>
       </c>
       <c r="N181" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>194</v>
       </c>
@@ -10829,10 +10910,10 @@
         <v>856</v>
       </c>
       <c r="N182" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>195</v>
       </c>
@@ -10873,10 +10954,10 @@
         <v>856</v>
       </c>
       <c r="N183" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>196</v>
       </c>
@@ -10917,10 +10998,10 @@
         <v>856</v>
       </c>
       <c r="N184" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="185" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>197</v>
       </c>
@@ -10958,10 +11039,10 @@
         <v>856</v>
       </c>
       <c r="N185" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>198</v>
       </c>
@@ -11002,10 +11083,10 @@
         <v>856</v>
       </c>
       <c r="N186" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="187" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -11046,10 +11127,10 @@
         <v>856</v>
       </c>
       <c r="N187" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>200</v>
       </c>
@@ -11090,10 +11171,10 @@
         <v>856</v>
       </c>
       <c r="N188" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>201</v>
       </c>
@@ -11134,10 +11215,10 @@
         <v>856</v>
       </c>
       <c r="N189" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>202</v>
       </c>
@@ -11178,10 +11259,10 @@
         <v>856</v>
       </c>
       <c r="N190" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>203</v>
       </c>
@@ -11222,10 +11303,10 @@
         <v>856</v>
       </c>
       <c r="N191" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>204</v>
       </c>
@@ -11266,10 +11347,10 @@
         <v>856</v>
       </c>
       <c r="N192" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>205</v>
       </c>
@@ -11310,10 +11391,10 @@
         <v>856</v>
       </c>
       <c r="N193" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>206</v>
       </c>
@@ -11351,10 +11432,10 @@
         <v>856</v>
       </c>
       <c r="N194" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>207</v>
       </c>
@@ -11395,10 +11476,10 @@
         <v>856</v>
       </c>
       <c r="N195" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="196" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>208</v>
       </c>
@@ -11439,10 +11520,10 @@
         <v>856</v>
       </c>
       <c r="N196" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="197" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>209</v>
       </c>
@@ -11483,10 +11564,10 @@
         <v>856</v>
       </c>
       <c r="N197" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="198" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>210</v>
       </c>
@@ -11527,10 +11608,10 @@
         <v>856</v>
       </c>
       <c r="N198" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>211</v>
       </c>
@@ -11571,10 +11652,10 @@
         <v>856</v>
       </c>
       <c r="N199" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>212</v>
       </c>
@@ -11615,10 +11696,10 @@
         <v>856</v>
       </c>
       <c r="N200" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>213</v>
       </c>
@@ -11659,10 +11740,10 @@
         <v>856</v>
       </c>
       <c r="N201" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>214</v>
       </c>
@@ -11703,10 +11784,10 @@
         <v>856</v>
       </c>
       <c r="N202" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>215</v>
       </c>
@@ -11747,10 +11828,10 @@
         <v>856</v>
       </c>
       <c r="N203" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>216</v>
       </c>
@@ -11791,10 +11872,10 @@
         <v>856</v>
       </c>
       <c r="N204" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>217</v>
       </c>
@@ -11835,10 +11916,10 @@
         <v>856</v>
       </c>
       <c r="N205" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>218</v>
       </c>
@@ -11879,10 +11960,10 @@
         <v>856</v>
       </c>
       <c r="N206" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>219</v>
       </c>
@@ -11923,10 +12004,10 @@
         <v>856</v>
       </c>
       <c r="N207" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>220</v>
       </c>
@@ -11967,10 +12048,10 @@
         <v>856</v>
       </c>
       <c r="N208" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>221</v>
       </c>
@@ -12011,10 +12092,10 @@
         <v>856</v>
       </c>
       <c r="N209" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>222</v>
       </c>
@@ -12055,10 +12136,10 @@
         <v>856</v>
       </c>
       <c r="N210" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>223</v>
       </c>
@@ -12099,10 +12180,10 @@
         <v>856</v>
       </c>
       <c r="N211" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="212" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>224</v>
       </c>
@@ -12143,10 +12224,10 @@
         <v>856</v>
       </c>
       <c r="N212" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>225</v>
       </c>
@@ -12187,10 +12268,10 @@
         <v>856</v>
       </c>
       <c r="N213" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>226</v>
       </c>
@@ -12231,10 +12312,10 @@
         <v>856</v>
       </c>
       <c r="N214" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>227</v>
       </c>
@@ -12275,10 +12356,10 @@
         <v>856</v>
       </c>
       <c r="N215" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>228</v>
       </c>
@@ -12319,10 +12400,10 @@
         <v>856</v>
       </c>
       <c r="N216" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>229</v>
       </c>
@@ -12363,10 +12444,10 @@
         <v>856</v>
       </c>
       <c r="N217" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>230</v>
       </c>
@@ -12407,10 +12488,10 @@
         <v>856</v>
       </c>
       <c r="N218" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="219" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>231</v>
       </c>
@@ -12451,10 +12532,10 @@
         <v>856</v>
       </c>
       <c r="N219" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>232</v>
       </c>
@@ -12495,10 +12576,10 @@
         <v>856</v>
       </c>
       <c r="N220" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>233</v>
       </c>
@@ -12536,10 +12617,10 @@
         <v>856</v>
       </c>
       <c r="N221" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>234</v>
       </c>
@@ -12580,10 +12661,10 @@
         <v>856</v>
       </c>
       <c r="N222" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>235</v>
       </c>
@@ -12624,10 +12705,10 @@
         <v>856</v>
       </c>
       <c r="N223" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>236</v>
       </c>
@@ -12668,10 +12749,10 @@
         <v>856</v>
       </c>
       <c r="N224" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>237</v>
       </c>
@@ -12712,10 +12793,10 @@
         <v>856</v>
       </c>
       <c r="N225" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="226" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>238</v>
       </c>
@@ -12756,10 +12837,10 @@
         <v>856</v>
       </c>
       <c r="N226" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="227" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>239</v>
       </c>
@@ -12800,10 +12881,10 @@
         <v>856</v>
       </c>
       <c r="N227" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="228" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>240</v>
       </c>
@@ -12844,10 +12925,10 @@
         <v>856</v>
       </c>
       <c r="N228" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="229" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>241</v>
       </c>
@@ -12885,10 +12966,10 @@
         <v>856</v>
       </c>
       <c r="N229" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="230" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>242</v>
       </c>
@@ -12929,10 +13010,10 @@
         <v>856</v>
       </c>
       <c r="N230" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="231" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>243</v>
       </c>
@@ -12973,10 +13054,10 @@
         <v>856</v>
       </c>
       <c r="N231" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="232" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>244</v>
       </c>
@@ -13017,10 +13098,10 @@
         <v>856</v>
       </c>
       <c r="N232" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="233" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>245</v>
       </c>
@@ -13061,10 +13142,10 @@
         <v>856</v>
       </c>
       <c r="N233" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="234" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>246</v>
       </c>
@@ -13105,10 +13186,10 @@
         <v>856</v>
       </c>
       <c r="N234" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="235" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>247</v>
       </c>
@@ -13149,10 +13230,10 @@
         <v>856</v>
       </c>
       <c r="N235" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="236" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>248</v>
       </c>
@@ -13193,10 +13274,10 @@
         <v>856</v>
       </c>
       <c r="N236" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="237" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>249</v>
       </c>
@@ -13237,10 +13318,10 @@
         <v>856</v>
       </c>
       <c r="N237" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="238" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>250</v>
       </c>
@@ -13281,10 +13362,10 @@
         <v>856</v>
       </c>
       <c r="N238" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="239" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>251</v>
       </c>
@@ -13325,10 +13406,10 @@
         <v>856</v>
       </c>
       <c r="N239" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="240" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>252</v>
       </c>
@@ -13366,10 +13447,10 @@
         <v>856</v>
       </c>
       <c r="N240" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="241" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>253</v>
       </c>
@@ -13410,10 +13491,10 @@
         <v>856</v>
       </c>
       <c r="N241" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="242" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>254</v>
       </c>
@@ -13454,10 +13535,10 @@
         <v>856</v>
       </c>
       <c r="N242" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="243" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>255</v>
       </c>
@@ -13498,10 +13579,10 @@
         <v>856</v>
       </c>
       <c r="N243" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="244" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>256</v>
       </c>
@@ -13542,10 +13623,10 @@
         <v>856</v>
       </c>
       <c r="N244" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="245" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>257</v>
       </c>
@@ -13586,10 +13667,10 @@
         <v>856</v>
       </c>
       <c r="N245" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="246" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>258</v>
       </c>
@@ -13630,10 +13711,10 @@
         <v>856</v>
       </c>
       <c r="N246" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="247" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>259</v>
       </c>
@@ -13674,10 +13755,10 @@
         <v>856</v>
       </c>
       <c r="N247" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="248" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>260</v>
       </c>
@@ -13718,10 +13799,10 @@
         <v>856</v>
       </c>
       <c r="N248" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="249" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>261</v>
       </c>
@@ -13762,10 +13843,10 @@
         <v>856</v>
       </c>
       <c r="N249" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>262</v>
       </c>
@@ -13806,10 +13887,10 @@
         <v>856</v>
       </c>
       <c r="N250" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="251" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>263</v>
       </c>
@@ -13850,10 +13931,10 @@
         <v>856</v>
       </c>
       <c r="N251" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="252" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>264</v>
       </c>
@@ -13894,10 +13975,10 @@
         <v>856</v>
       </c>
       <c r="N252" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="253" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>265</v>
       </c>
@@ -13938,10 +14019,10 @@
         <v>856</v>
       </c>
       <c r="N253" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>266</v>
       </c>
@@ -13982,10 +14063,10 @@
         <v>856</v>
       </c>
       <c r="N254" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="255" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>267</v>
       </c>
@@ -14026,10 +14107,10 @@
         <v>856</v>
       </c>
       <c r="N255" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>268</v>
       </c>
@@ -14070,10 +14151,10 @@
         <v>856</v>
       </c>
       <c r="N256" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>269</v>
       </c>
@@ -14114,10 +14195,10 @@
         <v>856</v>
       </c>
       <c r="N257" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>270</v>
       </c>
@@ -14158,10 +14239,10 @@
         <v>856</v>
       </c>
       <c r="N258" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>271</v>
       </c>
@@ -14202,10 +14283,10 @@
         <v>856</v>
       </c>
       <c r="N259" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="260" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>272</v>
       </c>
@@ -14246,10 +14327,10 @@
         <v>856</v>
       </c>
       <c r="N260" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="261" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>273</v>
       </c>
@@ -14290,10 +14371,10 @@
         <v>856</v>
       </c>
       <c r="N261" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="262" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>274</v>
       </c>
@@ -14334,10 +14415,10 @@
         <v>856</v>
       </c>
       <c r="N262" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="263" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>275</v>
       </c>
@@ -14378,10 +14459,10 @@
         <v>856</v>
       </c>
       <c r="N263" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="264" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>276</v>
       </c>
@@ -14422,10 +14503,10 @@
         <v>856</v>
       </c>
       <c r="N264" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="265" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>277</v>
       </c>
@@ -14463,10 +14544,10 @@
         <v>856</v>
       </c>
       <c r="N265" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>278</v>
       </c>
@@ -14507,10 +14588,10 @@
         <v>856</v>
       </c>
       <c r="N266" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="267" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>279</v>
       </c>
@@ -14551,10 +14632,10 @@
         <v>856</v>
       </c>
       <c r="N267" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="268" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>280</v>
       </c>
@@ -14595,10 +14676,10 @@
         <v>856</v>
       </c>
       <c r="N268" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="269" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>281</v>
       </c>
@@ -14636,10 +14717,10 @@
         <v>856</v>
       </c>
       <c r="N269" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="270" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>282</v>
       </c>
@@ -14680,10 +14761,10 @@
         <v>856</v>
       </c>
       <c r="N270" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="271" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>283</v>
       </c>
@@ -14724,10 +14805,10 @@
         <v>856</v>
       </c>
       <c r="N271" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="272" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>284</v>
       </c>
@@ -14768,10 +14849,10 @@
         <v>856</v>
       </c>
       <c r="N272" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="273" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>285</v>
       </c>
@@ -14812,10 +14893,10 @@
         <v>856</v>
       </c>
       <c r="N273" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="274" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>286</v>
       </c>
@@ -14856,10 +14937,10 @@
         <v>856</v>
       </c>
       <c r="N274" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="275" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>287</v>
       </c>
@@ -14900,10 +14981,10 @@
         <v>856</v>
       </c>
       <c r="N275" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="276" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>288</v>
       </c>
@@ -14944,10 +15025,10 @@
         <v>856</v>
       </c>
       <c r="N276" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="277" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>289</v>
       </c>
@@ -14988,10 +15069,10 @@
         <v>856</v>
       </c>
       <c r="N277" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="278" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>290</v>
       </c>
@@ -15032,10 +15113,10 @@
         <v>856</v>
       </c>
       <c r="N278" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="279" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>291</v>
       </c>
@@ -15076,10 +15157,10 @@
         <v>856</v>
       </c>
       <c r="N279" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>292</v>
       </c>
@@ -15120,10 +15201,10 @@
         <v>856</v>
       </c>
       <c r="N280" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="281" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>293</v>
       </c>
@@ -15164,10 +15245,10 @@
         <v>856</v>
       </c>
       <c r="N281" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="282" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>294</v>
       </c>
@@ -15208,10 +15289,10 @@
         <v>856</v>
       </c>
       <c r="N282" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="283" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>295</v>
       </c>
@@ -15252,10 +15333,10 @@
         <v>856</v>
       </c>
       <c r="N283" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="284" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>296</v>
       </c>
@@ -15296,10 +15377,10 @@
         <v>856</v>
       </c>
       <c r="N284" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="285" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>297</v>
       </c>
@@ -15340,10 +15421,10 @@
         <v>856</v>
       </c>
       <c r="N285" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="286" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>298</v>
       </c>
@@ -15384,10 +15465,10 @@
         <v>856</v>
       </c>
       <c r="N286" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="287" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>299</v>
       </c>
@@ -15428,10 +15509,10 @@
         <v>856</v>
       </c>
       <c r="N287" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="288" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>300</v>
       </c>
@@ -15472,10 +15553,10 @@
         <v>856</v>
       </c>
       <c r="N288" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="289" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>301</v>
       </c>
@@ -15516,10 +15597,10 @@
         <v>856</v>
       </c>
       <c r="N289" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="290" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>302</v>
       </c>
@@ -15560,10 +15641,10 @@
         <v>856</v>
       </c>
       <c r="N290" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="291" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>303</v>
       </c>
@@ -15604,10 +15685,10 @@
         <v>856</v>
       </c>
       <c r="N291" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="292" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>304</v>
       </c>
@@ -15648,10 +15729,10 @@
         <v>856</v>
       </c>
       <c r="N292" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="293" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>305</v>
       </c>
@@ -15692,10 +15773,10 @@
         <v>856</v>
       </c>
       <c r="N293" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="294" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>306</v>
       </c>
@@ -15736,10 +15817,10 @@
         <v>856</v>
       </c>
       <c r="N294" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="295" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>307</v>
       </c>
@@ -15780,10 +15861,10 @@
         <v>856</v>
       </c>
       <c r="N295" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="296" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>308</v>
       </c>
@@ -15824,10 +15905,10 @@
         <v>856</v>
       </c>
       <c r="N296" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="297" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>309</v>
       </c>
@@ -15868,10 +15949,10 @@
         <v>856</v>
       </c>
       <c r="N297" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="298" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>310</v>
       </c>
@@ -15912,10 +15993,10 @@
         <v>856</v>
       </c>
       <c r="N298" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="299" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>311</v>
       </c>
@@ -15956,10 +16037,10 @@
         <v>856</v>
       </c>
       <c r="N299" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="300" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>312</v>
       </c>
@@ -16000,10 +16081,10 @@
         <v>856</v>
       </c>
       <c r="N300" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="301" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>313</v>
       </c>
@@ -16044,10 +16125,10 @@
         <v>856</v>
       </c>
       <c r="N301" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="302" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>314</v>
       </c>
@@ -16085,10 +16166,10 @@
         <v>856</v>
       </c>
       <c r="N302" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="303" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>315</v>
       </c>
@@ -16129,10 +16210,10 @@
         <v>856</v>
       </c>
       <c r="N303" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="304" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>316</v>
       </c>
@@ -16173,10 +16254,10 @@
         <v>856</v>
       </c>
       <c r="N304" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="305" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>317</v>
       </c>
@@ -16217,10 +16298,10 @@
         <v>856</v>
       </c>
       <c r="N305" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="306" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>318</v>
       </c>
@@ -16261,10 +16342,10 @@
         <v>856</v>
       </c>
       <c r="N306" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="307" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>319</v>
       </c>
@@ -16305,10 +16386,10 @@
         <v>856</v>
       </c>
       <c r="N307" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="308" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>320</v>
       </c>
@@ -16349,10 +16430,10 @@
         <v>856</v>
       </c>
       <c r="N308" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="309" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>321</v>
       </c>
@@ -16393,10 +16474,10 @@
         <v>856</v>
       </c>
       <c r="N309" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="310" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>322</v>
       </c>
@@ -16437,10 +16518,10 @@
         <v>856</v>
       </c>
       <c r="N310" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="311" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>323</v>
       </c>
@@ -16481,10 +16562,10 @@
         <v>856</v>
       </c>
       <c r="N311" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="312" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>324</v>
       </c>
@@ -16525,10 +16606,10 @@
         <v>856</v>
       </c>
       <c r="N312" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="313" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>325</v>
       </c>
@@ -16569,10 +16650,10 @@
         <v>856</v>
       </c>
       <c r="N313" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="314" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>326</v>
       </c>
@@ -16613,10 +16694,10 @@
         <v>856</v>
       </c>
       <c r="N314" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="315" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>327</v>
       </c>
@@ -16657,10 +16738,10 @@
         <v>856</v>
       </c>
       <c r="N315" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="316" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>328</v>
       </c>
@@ -16701,10 +16782,10 @@
         <v>856</v>
       </c>
       <c r="N316" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="317" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>329</v>
       </c>
@@ -16745,10 +16826,10 @@
         <v>856</v>
       </c>
       <c r="N317" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="318" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>330</v>
       </c>
@@ -16789,10 +16870,10 @@
         <v>856</v>
       </c>
       <c r="N318" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="319" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>331</v>
       </c>
@@ -16833,10 +16914,10 @@
         <v>856</v>
       </c>
       <c r="N319" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="320" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>332</v>
       </c>
@@ -16877,10 +16958,10 @@
         <v>856</v>
       </c>
       <c r="N320" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="321" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>333</v>
       </c>
@@ -16921,10 +17002,10 @@
         <v>856</v>
       </c>
       <c r="N321" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="322" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>334</v>
       </c>
@@ -16965,10 +17046,10 @@
         <v>856</v>
       </c>
       <c r="N322" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="323" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>335</v>
       </c>
@@ -17009,10 +17090,10 @@
         <v>856</v>
       </c>
       <c r="N323" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="324" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>336</v>
       </c>
@@ -17053,10 +17134,10 @@
         <v>856</v>
       </c>
       <c r="N324" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="325" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>337</v>
       </c>
@@ -17097,10 +17178,10 @@
         <v>856</v>
       </c>
       <c r="N325" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="326" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>338</v>
       </c>
@@ -17141,10 +17222,10 @@
         <v>856</v>
       </c>
       <c r="N326" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="327" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>339</v>
       </c>
@@ -17185,10 +17266,10 @@
         <v>856</v>
       </c>
       <c r="N327" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="328" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>340</v>
       </c>
@@ -17229,10 +17310,10 @@
         <v>856</v>
       </c>
       <c r="N328" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="329" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>341</v>
       </c>
@@ -17273,10 +17354,10 @@
         <v>856</v>
       </c>
       <c r="N329" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="330" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>342</v>
       </c>
@@ -17317,10 +17398,10 @@
         <v>856</v>
       </c>
       <c r="N330" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="331" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>343</v>
       </c>
@@ -17361,10 +17442,10 @@
         <v>856</v>
       </c>
       <c r="N331" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="332" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>344</v>
       </c>
@@ -17405,10 +17486,10 @@
         <v>856</v>
       </c>
       <c r="N332" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="333" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>345</v>
       </c>
@@ -17449,10 +17530,10 @@
         <v>856</v>
       </c>
       <c r="N333" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="334" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>346</v>
       </c>
@@ -17493,10 +17574,10 @@
         <v>856</v>
       </c>
       <c r="N334" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="335" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>347</v>
       </c>
@@ -17537,10 +17618,10 @@
         <v>856</v>
       </c>
       <c r="N335" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="336" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>348</v>
       </c>
@@ -17581,10 +17662,10 @@
         <v>856</v>
       </c>
       <c r="N336" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="337" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>349</v>
       </c>
@@ -17625,10 +17706,10 @@
         <v>856</v>
       </c>
       <c r="N337" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="338" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>350</v>
       </c>
@@ -17669,10 +17750,10 @@
         <v>856</v>
       </c>
       <c r="N338" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="339" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>351</v>
       </c>
@@ -17713,10 +17794,10 @@
         <v>856</v>
       </c>
       <c r="N339" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="340" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>352</v>
       </c>
@@ -17757,10 +17838,10 @@
         <v>856</v>
       </c>
       <c r="N340" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="341" spans="1:14">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>353</v>
       </c>
@@ -17773,6 +17854,9 @@
       <c r="D341" t="s">
         <v>851</v>
       </c>
+      <c r="E341">
+        <v>40</v>
+      </c>
       <c r="F341" t="s">
         <v>853</v>
       </c>
@@ -17785,17 +17869,31 @@
       <c r="I341" s="1">
         <v>46251</v>
       </c>
+      <c r="J341" s="2">
+        <v>46260</v>
+      </c>
+      <c r="K341">
+        <f>J341-I341</f>
+        <v>9</v>
+      </c>
       <c r="L341" t="s">
         <v>854</v>
       </c>
       <c r="M341" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N341" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N341" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Ken Follett"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>